--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.4516,0.1136,0.1041,0.4534</t>
-  </si>
-  <si>
-    <t>0.0036,0.0245,0.0014,0.9967</t>
-  </si>
-  <si>
-    <t>0.3435,0.1303,0.0356,0.6650</t>
-  </si>
-  <si>
-    <t>0.2722,0.0310,0.0267,0.7952</t>
-  </si>
-  <si>
-    <t>0.9864,0.0080,0.0015,0.0036</t>
-  </si>
-  <si>
-    <t>0.9819,0.0117,0.0024,0.0044</t>
-  </si>
-  <si>
-    <t>0.9485,0.0600,0.0072,0.0060</t>
-  </si>
-  <si>
-    <t>0.9759,0.0145,0.0035,0.0060</t>
-  </si>
-  <si>
-    <t>0.9505,0.0555,0.0055,0.0054</t>
-  </si>
-  <si>
-    <t>0.9520,0.0584,0.0057,0.0041</t>
-  </si>
-  <si>
-    <t>0.9797,0.0154,0.0027,0.0032</t>
-  </si>
-  <si>
-    <t>0.9776,0.0162,0.0031,0.0044</t>
-  </si>
-  <si>
-    <t>0.4992,0.1503,0.1781,0.3360</t>
-  </si>
-  <si>
-    <t>0.1357,0.1403,0.8024,0.0248</t>
-  </si>
-  <si>
-    <t>0.1695,0.0394,0.8494,0.0200</t>
-  </si>
-  <si>
-    <t>0.2425,0.0752,0.7119,0.0520</t>
-  </si>
-  <si>
-    <t>0.6542,0.1406,0.2260,0.0354</t>
-  </si>
-  <si>
-    <t>0.0286,0.9579,0.0095,0.0039</t>
-  </si>
-  <si>
-    <t>0.0426,0.9451,0.0185,0.0022</t>
-  </si>
-  <si>
-    <t>0.0382,0.9480,0.0079,0.0059</t>
-  </si>
-  <si>
-    <t>0.0393,0.9400,0.0285,0.0038</t>
-  </si>
-  <si>
-    <t>0.0079,0.9840,0.0097,0.0011</t>
-  </si>
-  <si>
-    <t>0.2426,0.2694,0.3929,0.2718</t>
-  </si>
-  <si>
-    <t>0.2898,0.0533,0.5608,0.1635</t>
-  </si>
-  <si>
-    <t>0.0184,0.0795,0.9498,0.0143</t>
-  </si>
-  <si>
-    <t>0.2174,0.1295,0.6564,0.1238</t>
-  </si>
-  <si>
-    <t>0.1120,0.0340,0.8766,0.0353</t>
-  </si>
-  <si>
-    <t>0.1307,0.0407,0.8393,0.0571</t>
-  </si>
-  <si>
-    <t>0.0402,0.0626,0.9072,0.0507</t>
-  </si>
-  <si>
-    <t>0.1367,0.8568,0.0245,0.0056</t>
-  </si>
-  <si>
-    <t>0.5870,0.3711,0.0809,0.0523</t>
-  </si>
-  <si>
-    <t>0.0366,0.0737,0.9120,0.0400</t>
-  </si>
-  <si>
-    <t>0.1641,0.6839,0.2227,0.0130</t>
-  </si>
-  <si>
-    <t>0.6611,0.2855,0.0520,0.0682</t>
-  </si>
-  <si>
-    <t>0.2202,0.6835,0.1581,0.0703</t>
-  </si>
-  <si>
-    <t>0.5607,0.4942,0.0200,0.0160</t>
-  </si>
-  <si>
-    <t>0.1012,0.7254,0.3093,0.0119</t>
-  </si>
-  <si>
-    <t>0.0039,0.9284,0.0933,0.1433</t>
-  </si>
-  <si>
-    <t>0.0323,0.0739,0.7403,0.2907</t>
-  </si>
-  <si>
-    <t>0.0309,0.2125,0.7980,0.1059</t>
-  </si>
-  <si>
-    <t>0.0507,0.0443,0.7990,0.2207</t>
-  </si>
-  <si>
-    <t>0.0612,0.5232,0.6909,0.0457</t>
-  </si>
-  <si>
-    <t>0.0091,0.9400,0.0649,0.0542</t>
-  </si>
-  <si>
-    <t>0.0248,0.2978,0.8916,0.0172</t>
-  </si>
-  <si>
-    <t>0.0799,0.5685,0.0241,0.6489</t>
-  </si>
-  <si>
-    <t>0.0172,0.9606,0.0319,0.0064</t>
-  </si>
-  <si>
-    <t>0.0158,0.9147,0.2766,0.0143</t>
-  </si>
-  <si>
-    <t>0.0163,0.9558,0.0955,0.0045</t>
-  </si>
-  <si>
-    <t>0.0052,0.2297,0.9359,0.0217</t>
-  </si>
-  <si>
-    <t>0.0102,0.4698,0.9122,0.0064</t>
-  </si>
-  <si>
-    <t>0.0205,0.0141,0.7913,0.3363</t>
-  </si>
-  <si>
-    <t>0.1066,0.0094,0.8932,0.0291</t>
-  </si>
-  <si>
-    <t>0.0162,0.3188,0.8440,0.0313</t>
-  </si>
-  <si>
-    <t>0.0348,0.0669,0.9184,0.0363</t>
-  </si>
-  <si>
-    <t>0.7521,0.3445,0.0138,0.0067</t>
-  </si>
-  <si>
-    <t>0.9487,0.0385,0.0104,0.0120</t>
-  </si>
-  <si>
-    <t>0.9326,0.0616,0.0099,0.0117</t>
-  </si>
-  <si>
-    <t>0.0120,0.3089,0.9503,0.0056</t>
-  </si>
-  <si>
-    <t>0.8409,0.2030,0.0211,0.0075</t>
-  </si>
-  <si>
-    <t>0.9538,0.0499,0.0045,0.0049</t>
-  </si>
-  <si>
-    <t>0.9387,0.0734,0.0083,0.0056</t>
-  </si>
-  <si>
-    <t>0.0121,0.8969,0.3486,0.0355</t>
-  </si>
-  <si>
-    <t>0.0123,0.2964,0.8917,0.0300</t>
-  </si>
-  <si>
-    <t>0.0091,0.0583,0.9507,0.0363</t>
-  </si>
-  <si>
-    <t>0.0070,0.8855,0.7092,0.0066</t>
-  </si>
-  <si>
-    <t>0.0116,0.0684,0.9585,0.0174</t>
-  </si>
-  <si>
-    <t>0.1328,0.8134,0.0606,0.0210</t>
-  </si>
-  <si>
-    <t>0.0059,0.9844,0.0027,0.0025</t>
-  </si>
-  <si>
-    <t>0.5397,0.2018,0.3238,0.0212</t>
-  </si>
-  <si>
-    <t>0.1710,0.7048,0.1474,0.0119</t>
-  </si>
-  <si>
-    <t>0.1100,0.6611,0.2672,0.0703</t>
-  </si>
-  <si>
-    <t>0.0237,0.7973,0.6005,0.0153</t>
-  </si>
-  <si>
-    <t>0.0211,0.6050,0.8334,0.0084</t>
-  </si>
-  <si>
-    <t>0.0060,0.9497,0.1782,0.0203</t>
-  </si>
-  <si>
-    <t>0.0101,0.9303,0.2524,0.0140</t>
-  </si>
-  <si>
-    <t>0.0172,0.0331,0.0072,0.9859</t>
-  </si>
-  <si>
-    <t>0.0038,0.0151,0.0013,0.9968</t>
-  </si>
-  <si>
-    <t>0.0103,0.0306,0.0049,0.9910</t>
-  </si>
-  <si>
-    <t>0.0113,0.0481,0.0033,0.9909</t>
-  </si>
-  <si>
-    <t>0.0147,0.0203,0.0098,0.9862</t>
-  </si>
-  <si>
-    <t>0.0070,0.0210,0.0028,0.9943</t>
-  </si>
-  <si>
-    <t>0.0388,0.7779,0.3575,0.0660</t>
-  </si>
-  <si>
-    <t>0.0185,0.7756,0.6874,0.0169</t>
-  </si>
-  <si>
-    <t>0.0341,0.6379,0.6902,0.0338</t>
-  </si>
-  <si>
-    <t>0.0303,0.5947,0.8030,0.0165</t>
-  </si>
-  <si>
-    <t>0.0126,0.9152,0.3094,0.0147</t>
-  </si>
-  <si>
-    <t>0.0226,0.8717,0.2866,0.0307</t>
-  </si>
-  <si>
-    <t>0.9372,0.0768,0.0088,0.0054</t>
-  </si>
-  <si>
-    <t>0.9078,0.1223,0.0086,0.0051</t>
-  </si>
-  <si>
-    <t>0.9628,0.0397,0.0049,0.0039</t>
-  </si>
-  <si>
-    <t>0.9797,0.0127,0.0029,0.0048</t>
-  </si>
-  <si>
-    <t>0.9468,0.0594,0.0054,0.0068</t>
-  </si>
-  <si>
-    <t>0.9687,0.0265,0.0046,0.0050</t>
-  </si>
-  <si>
-    <t>0.9600,0.0487,0.0046,0.0040</t>
-  </si>
-  <si>
-    <t>0.9315,0.0795,0.0093,0.0062</t>
-  </si>
-  <si>
-    <t>0.9802,0.0118,0.0030,0.0052</t>
-  </si>
-  <si>
-    <t>0.9817,0.0126,0.0023,0.0037</t>
-  </si>
-  <si>
-    <t>0.9831,0.0085,0.0020,0.0058</t>
-  </si>
-  <si>
-    <t>0.9840,0.0104,0.0018,0.0035</t>
-  </si>
-  <si>
-    <t>0.9798,0.0119,0.0026,0.0047</t>
-  </si>
-  <si>
-    <t>0.9308,0.0700,0.0086,0.0108</t>
-  </si>
-  <si>
-    <t>0.9851,0.0071,0.0019,0.0055</t>
-  </si>
-  <si>
-    <t>0.9751,0.0228,0.0029,0.0035</t>
-  </si>
-  <si>
-    <t>0.0020,0.0126,0.9863,0.0172</t>
-  </si>
-  <si>
-    <t>0.1694,0.1244,0.7221,0.0753</t>
-  </si>
-  <si>
-    <t>0.1669,0.1479,0.1496,0.7209</t>
-  </si>
-  <si>
-    <t>0.3164,0.0647,0.6820,0.0402</t>
-  </si>
-  <si>
-    <t>0.0539,0.9249,0.0227,0.0061</t>
-  </si>
-  <si>
-    <t>0.0276,0.9591,0.0108,0.0036</t>
-  </si>
-  <si>
-    <t>0.0489,0.9378,0.0128,0.0050</t>
-  </si>
-  <si>
-    <t>0.0520,0.9375,0.0118,0.0051</t>
-  </si>
-  <si>
-    <t>0.0158,0.9695,0.0139,0.0025</t>
-  </si>
-  <si>
-    <t>0.0144,0.9769,0.0047,0.0021</t>
-  </si>
-  <si>
-    <t>0.2203,0.8168,0.0165,0.0045</t>
-  </si>
-  <si>
-    <t>0.7422,0.1083,0.1351,0.0425</t>
-  </si>
-  <si>
-    <t>0.1719,0.1054,0.7899,0.0313</t>
-  </si>
-  <si>
-    <t>0.2262,0.6178,0.1730,0.0829</t>
-  </si>
-  <si>
-    <t>0.4772,0.1348,0.4115,0.0784</t>
-  </si>
-  <si>
-    <t>0.1320,0.2515,0.0409,0.8494</t>
-  </si>
-  <si>
-    <t>0.0233,0.9565,0.0425,0.0052</t>
-  </si>
-  <si>
-    <t>0.0239,0.9443,0.0340,0.0203</t>
-  </si>
-  <si>
-    <t>0.0811,0.8603,0.0364,0.0373</t>
-  </si>
-  <si>
-    <t>0.0193,0.9098,0.2358,0.0118</t>
-  </si>
-  <si>
-    <t>0.0709,0.8688,0.1541,0.0063</t>
-  </si>
-  <si>
-    <t>0.3886,0.6887,0.0231,0.0064</t>
-  </si>
-  <si>
-    <t>0.6751,0.3859,0.0266,0.0126</t>
-  </si>
-  <si>
-    <t>0.9567,0.0214,0.0098,0.0153</t>
-  </si>
-  <si>
-    <t>0.9451,0.0577,0.0070,0.0078</t>
-  </si>
-  <si>
-    <t>0.9584,0.0253,0.0078,0.0115</t>
-  </si>
-  <si>
-    <t>0.9301,0.0511,0.0158,0.0159</t>
-  </si>
-  <si>
-    <t>0.9623,0.0264,0.0062,0.0094</t>
-  </si>
-  <si>
-    <t>0.7516,0.0899,0.2025,0.0329</t>
-  </si>
-  <si>
-    <t>0.9721,0.0108,0.0028,0.0125</t>
-  </si>
-  <si>
-    <t>0.9195,0.0519,0.0201,0.0212</t>
-  </si>
-  <si>
-    <t>0.0270,0.7911,0.5781,0.0275</t>
-  </si>
-  <si>
-    <t>0.0267,0.5990,0.8064,0.0165</t>
-  </si>
-  <si>
-    <t>0.0291,0.5828,0.7897,0.0115</t>
-  </si>
-  <si>
-    <t>0.0939,0.1632,0.8235,0.0361</t>
-  </si>
-  <si>
-    <t>0.1266,0.6322,0.0307,0.4471</t>
-  </si>
-  <si>
-    <t>0.2549,0.5192,0.2646,0.1249</t>
-  </si>
-  <si>
-    <t>0.2893,0.0259,0.7465,0.0287</t>
-  </si>
-  <si>
-    <t>0.2865,0.5869,0.1169,0.1171</t>
-  </si>
-  <si>
-    <t>0.0263,0.0210,0.0050,0.9839</t>
-  </si>
-  <si>
-    <t>0.0013,0.0081,0.0009,0.9986</t>
-  </si>
-  <si>
-    <t>0.0074,0.0508,0.0072,0.9907</t>
-  </si>
-  <si>
-    <t>0.0151,0.0193,0.0038,0.9897</t>
-  </si>
-  <si>
-    <t>0.0107,0.8382,0.5609,0.0240</t>
-  </si>
-  <si>
-    <t>0.8960,0.1289,0.0143,0.0104</t>
-  </si>
-  <si>
-    <t>0.0955,0.8801,0.0142,0.0161</t>
-  </si>
-  <si>
-    <t>0.9626,0.0219,0.0044,0.0117</t>
-  </si>
-  <si>
-    <t>0.2886,0.7416,0.0225,0.0160</t>
-  </si>
-  <si>
-    <t>0.9167,0.0340,0.0140,0.0381</t>
-  </si>
-  <si>
-    <t>0.1740,0.0465,0.0208,0.8868</t>
-  </si>
-  <si>
-    <t>0.9523,0.0197,0.0054,0.0221</t>
-  </si>
-  <si>
-    <t>0.0027,0.1396,0.2731,0.7612</t>
-  </si>
-  <si>
-    <t>0.8177,0.0208,0.0172,0.1691</t>
-  </si>
-  <si>
-    <t>0.8600,0.0664,0.0335,0.0647</t>
-  </si>
-  <si>
-    <t>0.2376,0.7723,0.0169,0.0165</t>
-  </si>
-  <si>
-    <t>0.5484,0.4364,0.0801,0.0314</t>
-  </si>
-  <si>
-    <t>0.2721,0.7116,0.0463,0.0306</t>
-  </si>
-  <si>
-    <t>0.2832,0.6721,0.0686,0.0452</t>
-  </si>
-  <si>
-    <t>0.7015,0.2789,0.0812,0.0199</t>
-  </si>
-  <si>
-    <t>0.3238,0.6354,0.0999,0.0373</t>
-  </si>
-  <si>
-    <t>0.9811,0.0112,0.0037,0.0041</t>
-  </si>
-  <si>
-    <t>0.9572,0.0368,0.0052,0.0081</t>
-  </si>
-  <si>
-    <t>0.9770,0.0133,0.0029,0.0073</t>
-  </si>
-  <si>
-    <t>0.9545,0.0385,0.0062,0.0108</t>
-  </si>
-  <si>
-    <t>0.9549,0.0357,0.0053,0.0097</t>
-  </si>
-  <si>
-    <t>0.9381,0.0538,0.0065,0.0126</t>
-  </si>
-  <si>
-    <t>0.9738,0.0144,0.0037,0.0074</t>
-  </si>
-  <si>
-    <t>0.9526,0.0288,0.0063,0.0138</t>
-  </si>
-  <si>
-    <t>0.3011,0.7291,0.0344,0.0117</t>
-  </si>
-  <si>
-    <t>0.6259,0.3842,0.0545,0.0117</t>
-  </si>
-  <si>
-    <t>0.3079,0.7314,0.0271,0.0090</t>
-  </si>
-  <si>
-    <t>0.9100,0.0472,0.0336,0.0192</t>
-  </si>
-  <si>
-    <t>0.6992,0.3657,0.0115,0.0091</t>
-  </si>
-  <si>
-    <t>0.9153,0.0788,0.0138,0.0131</t>
-  </si>
-  <si>
-    <t>0.8626,0.1724,0.0119,0.0096</t>
-  </si>
-  <si>
-    <t>0.3915,0.6342,0.0199,0.0259</t>
-  </si>
-  <si>
-    <t>0.0085,0.0809,0.9810,0.0040</t>
-  </si>
-  <si>
-    <t>0.7233,0.3517,0.0123,0.0102</t>
-  </si>
-  <si>
-    <t>0.0190,0.0488,0.9584,0.0152</t>
-  </si>
-  <si>
-    <t>0.0124,0.0777,0.9646,0.0102</t>
-  </si>
-  <si>
-    <t>0.0836,0.0581,0.8967,0.0263</t>
-  </si>
-  <si>
-    <t>0.0524,0.2113,0.7133,0.1710</t>
-  </si>
-  <si>
-    <t>0.0768,0.1979,0.8616,0.0176</t>
-  </si>
-  <si>
-    <t>0.0558,0.0795,0.9279,0.0099</t>
-  </si>
-  <si>
-    <t>0.0691,0.0689,0.9055,0.0252</t>
-  </si>
-  <si>
-    <t>0.3037,0.2160,0.5379,0.0508</t>
-  </si>
-  <si>
-    <t>0.1626,0.0604,0.8211,0.0380</t>
-  </si>
-  <si>
-    <t>0.1175,0.5479,0.1011,0.5598</t>
-  </si>
-  <si>
-    <t>0.2132,0.3277,0.5000,0.0793</t>
-  </si>
-  <si>
-    <t>0.1918,0.7160,0.1106,0.0651</t>
-  </si>
-  <si>
-    <t>0.3784,0.1711,0.4292,0.0714</t>
-  </si>
-  <si>
-    <t>0.3104,0.4833,0.1599,0.1588</t>
-  </si>
-  <si>
-    <t>0.4057,0.4654,0.1638,0.0494</t>
-  </si>
-  <si>
-    <t>0.5615,0.5450,0.0181,0.0063</t>
-  </si>
-  <si>
-    <t>0.4995,0.6096,0.0146,0.0045</t>
-  </si>
-  <si>
-    <t>0.4621,0.6238,0.0241,0.0050</t>
-  </si>
-  <si>
-    <t>0.9440,0.0644,0.0068,0.0041</t>
-  </si>
-  <si>
-    <t>0.4024,0.6683,0.0120,0.0084</t>
-  </si>
-  <si>
-    <t>0.1888,0.5350,0.3261,0.1086</t>
-  </si>
-  <si>
-    <t>0.6043,0.1907,0.2090,0.1188</t>
-  </si>
-  <si>
-    <t>0.3127,0.0909,0.1317,0.6100</t>
-  </si>
-  <si>
-    <t>0.3670,0.1152,0.4929,0.1544</t>
-  </si>
-  <si>
-    <t>0.1163,0.6880,0.0327,0.3610</t>
-  </si>
-  <si>
-    <t>0.0546,0.1148,0.5214,0.4802</t>
-  </si>
-  <si>
-    <t>0.0954,0.4989,0.4171,0.2238</t>
-  </si>
-  <si>
-    <t>0.0699,0.4000,0.6232,0.1430</t>
-  </si>
-  <si>
-    <t>0.0750,0.3342,0.7006,0.0975</t>
-  </si>
-  <si>
-    <t>0.0718,0.2768,0.7887,0.0678</t>
-  </si>
-  <si>
-    <t>0.9544,0.0368,0.0073,0.0081</t>
-  </si>
-  <si>
-    <t>0.9604,0.0355,0.0055,0.0054</t>
-  </si>
-  <si>
-    <t>0.9789,0.0141,0.0027,0.0052</t>
-  </si>
-  <si>
-    <t>0.9521,0.0493,0.0066,0.0053</t>
-  </si>
-  <si>
-    <t>0.9507,0.0624,0.0063,0.0040</t>
-  </si>
-  <si>
-    <t>0.9693,0.0269,0.0041,0.0056</t>
-  </si>
-  <si>
-    <t>0.9728,0.0215,0.0035,0.0050</t>
-  </si>
-  <si>
-    <t>0.9555,0.0355,0.0066,0.0078</t>
-  </si>
-  <si>
-    <t>0.1579,0.0545,0.8325,0.0289</t>
-  </si>
-  <si>
-    <t>0.6293,0.2392,0.1843,0.0335</t>
-  </si>
-  <si>
-    <t>0.6515,0.1450,0.2468,0.0524</t>
-  </si>
-  <si>
-    <t>0.0315,0.0340,0.9447,0.0231</t>
-  </si>
-  <si>
-    <t>0.0120,0.1827,0.8839,0.0517</t>
-  </si>
-  <si>
-    <t>0.0659,0.1836,0.8734,0.0158</t>
-  </si>
-  <si>
-    <t>0.0079,0.0364,0.9672,0.0273</t>
-  </si>
-  <si>
-    <t>0.0939,0.0768,0.8720,0.0245</t>
-  </si>
-  <si>
-    <t>0.0265,0.1932,0.8269,0.1076</t>
-  </si>
-  <si>
-    <t>0.0630,0.3071,0.8248,0.0311</t>
-  </si>
-  <si>
-    <t>0.2054,0.1787,0.5151,0.2548</t>
-  </si>
-  <si>
-    <t>0.3633,0.0327,0.4484,0.1678</t>
-  </si>
-  <si>
-    <t>0.2778,0.1390,0.5841,0.0788</t>
-  </si>
-  <si>
-    <t>0.5112,0.1007,0.2202,0.2754</t>
-  </si>
-  <si>
-    <t>0.9530,0.0436,0.0070,0.0080</t>
-  </si>
-  <si>
-    <t>0.9604,0.0365,0.0051,0.0073</t>
-  </si>
-  <si>
-    <t>0.9695,0.0242,0.0057,0.0049</t>
-  </si>
-  <si>
-    <t>0.9346,0.0819,0.0097,0.0048</t>
-  </si>
-  <si>
-    <t>0.9826,0.0101,0.0030,0.0043</t>
-  </si>
-  <si>
-    <t>0.8664,0.1817,0.0124,0.0055</t>
-  </si>
-  <si>
-    <t>0.9714,0.0213,0.0042,0.0057</t>
-  </si>
-  <si>
-    <t>0.9464,0.0518,0.0087,0.0082</t>
-  </si>
-  <si>
-    <t>0.0551,0.5410,0.6116,0.0622</t>
-  </si>
-  <si>
-    <t>0.0336,0.4458,0.8213,0.0223</t>
-  </si>
-  <si>
-    <t>0.0510,0.2540,0.6786,0.1733</t>
-  </si>
-  <si>
-    <t>0.1018,0.0730,0.7996,0.1184</t>
-  </si>
-  <si>
-    <t>0.0096,0.0126,0.9440,0.0869</t>
-  </si>
-  <si>
-    <t>0.0606,0.0670,0.0952,0.8996</t>
-  </si>
-  <si>
-    <t>0.2291,0.1907,0.6047,0.0962</t>
-  </si>
-  <si>
-    <t>0.0730,0.2074,0.5166,0.3769</t>
-  </si>
-  <si>
-    <t>0.8760,0.0490,0.0339,0.0538</t>
-  </si>
-  <si>
-    <t>0.0070,0.0515,0.0029,0.9930</t>
-  </si>
-  <si>
-    <t>0.0111,0.0153,0.0048,0.9913</t>
-  </si>
-  <si>
-    <t>0.0033,0.0103,0.0014,0.9972</t>
-  </si>
-  <si>
-    <t>0.0050,0.0152,0.0037,0.9947</t>
-  </si>
-  <si>
-    <t>0.0368,0.0622,0.0155,0.9686</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.0423,0.2358,0.0221,0.9349</t>
+  </si>
+  <si>
+    <t>0.0065,0.0209,0.0033,0.9941</t>
+  </si>
+  <si>
+    <t>0.5758,0.1300,0.0175,0.3168</t>
+  </si>
+  <si>
+    <t>0.0408,0.0411,0.0097,0.9731</t>
+  </si>
+  <si>
+    <t>0.9765,0.0150,0.0031,0.0060</t>
+  </si>
+  <si>
+    <t>0.9645,0.0337,0.0050,0.0042</t>
+  </si>
+  <si>
+    <t>0.9775,0.0135,0.0039,0.0054</t>
+  </si>
+  <si>
+    <t>0.9781,0.0147,0.0029,0.0061</t>
+  </si>
+  <si>
+    <t>0.9627,0.0352,0.0052,0.0057</t>
+  </si>
+  <si>
+    <t>0.9280,0.1090,0.0066,0.0037</t>
+  </si>
+  <si>
+    <t>0.9837,0.0083,0.0021,0.0056</t>
+  </si>
+  <si>
+    <t>0.9838,0.0062,0.0016,0.0068</t>
+  </si>
+  <si>
+    <t>0.2692,0.0542,0.5089,0.2296</t>
+  </si>
+  <si>
+    <t>0.2350,0.0450,0.8096,0.0156</t>
+  </si>
+  <si>
+    <t>0.1456,0.0291,0.8571,0.0354</t>
+  </si>
+  <si>
+    <t>0.2170,0.1171,0.7348,0.0285</t>
+  </si>
+  <si>
+    <t>0.4165,0.0994,0.5497,0.0495</t>
+  </si>
+  <si>
+    <t>0.0214,0.9692,0.0076,0.0021</t>
+  </si>
+  <si>
+    <t>0.0159,0.9719,0.0111,0.0034</t>
+  </si>
+  <si>
+    <t>0.4190,0.6315,0.0172,0.0116</t>
+  </si>
+  <si>
+    <t>0.0167,0.9699,0.0109,0.0030</t>
+  </si>
+  <si>
+    <t>0.0132,0.9769,0.0091,0.0018</t>
+  </si>
+  <si>
+    <t>0.3587,0.0342,0.5646,0.0904</t>
+  </si>
+  <si>
+    <t>0.1736,0.3400,0.5362,0.0534</t>
+  </si>
+  <si>
+    <t>0.0171,0.0361,0.9666,0.0111</t>
+  </si>
+  <si>
+    <t>0.2018,0.3334,0.4770,0.0483</t>
+  </si>
+  <si>
+    <t>0.1629,0.0139,0.8666,0.0246</t>
+  </si>
+  <si>
+    <t>0.2302,0.1050,0.6425,0.1653</t>
+  </si>
+  <si>
+    <t>0.0438,0.0548,0.9197,0.0331</t>
+  </si>
+  <si>
+    <t>0.0671,0.9082,0.0238,0.0080</t>
+  </si>
+  <si>
+    <t>0.5465,0.3162,0.1930,0.0373</t>
+  </si>
+  <si>
+    <t>0.0068,0.0687,0.9641,0.0228</t>
+  </si>
+  <si>
+    <t>0.1951,0.5503,0.3414,0.0249</t>
+  </si>
+  <si>
+    <t>0.5940,0.3491,0.0195,0.0752</t>
+  </si>
+  <si>
+    <t>0.5475,0.3456,0.1720,0.0378</t>
+  </si>
+  <si>
+    <t>0.3776,0.6806,0.0219,0.0077</t>
+  </si>
+  <si>
+    <t>0.1613,0.8018,0.0840,0.0100</t>
+  </si>
+  <si>
+    <t>0.0105,0.9102,0.0558,0.1478</t>
+  </si>
+  <si>
+    <t>0.0106,0.1193,0.5785,0.4455</t>
+  </si>
+  <si>
+    <t>0.0392,0.1728,0.6273,0.2717</t>
+  </si>
+  <si>
+    <t>0.0416,0.0748,0.8045,0.1658</t>
+  </si>
+  <si>
+    <t>0.0622,0.2807,0.6935,0.1372</t>
+  </si>
+  <si>
+    <t>0.0087,0.9281,0.0644,0.1067</t>
+  </si>
+  <si>
+    <t>0.0285,0.1078,0.9297,0.0208</t>
+  </si>
+  <si>
+    <t>0.0821,0.7555,0.0275,0.3413</t>
+  </si>
+  <si>
+    <t>0.0209,0.9588,0.0222,0.0086</t>
+  </si>
+  <si>
+    <t>0.0130,0.9341,0.1882,0.0056</t>
+  </si>
+  <si>
+    <t>0.0202,0.9505,0.0637,0.0066</t>
+  </si>
+  <si>
+    <t>0.0367,0.4856,0.7776,0.0452</t>
+  </si>
+  <si>
+    <t>0.0166,0.3149,0.9187,0.0128</t>
+  </si>
+  <si>
+    <t>0.0514,0.0286,0.8763,0.1078</t>
+  </si>
+  <si>
+    <t>0.1027,0.0267,0.8241,0.1050</t>
+  </si>
+  <si>
+    <t>0.0120,0.0481,0.9555,0.0263</t>
+  </si>
+  <si>
+    <t>0.0339,0.1498,0.9256,0.0112</t>
+  </si>
+  <si>
+    <t>0.9258,0.0787,0.0117,0.0089</t>
+  </si>
+  <si>
+    <t>0.9521,0.0400,0.0080,0.0094</t>
+  </si>
+  <si>
+    <t>0.9553,0.0351,0.0074,0.0096</t>
+  </si>
+  <si>
+    <t>0.0192,0.0985,0.9406,0.0297</t>
+  </si>
+  <si>
+    <t>0.9480,0.0629,0.0079,0.0048</t>
+  </si>
+  <si>
+    <t>0.9524,0.0526,0.0073,0.0046</t>
+  </si>
+  <si>
+    <t>0.8258,0.2288,0.0156,0.0086</t>
+  </si>
+  <si>
+    <t>0.0189,0.8865,0.3055,0.0359</t>
+  </si>
+  <si>
+    <t>0.0256,0.1442,0.8324,0.1184</t>
+  </si>
+  <si>
+    <t>0.0091,0.0224,0.8969,0.1602</t>
+  </si>
+  <si>
+    <t>0.0178,0.8873,0.3555,0.0207</t>
+  </si>
+  <si>
+    <t>0.0226,0.1415,0.9100,0.0345</t>
+  </si>
+  <si>
+    <t>0.1040,0.7987,0.1376,0.0123</t>
+  </si>
+  <si>
+    <t>0.0090,0.9814,0.0071,0.0017</t>
+  </si>
+  <si>
+    <t>0.6235,0.3011,0.0531,0.0977</t>
+  </si>
+  <si>
+    <t>0.3635,0.6347,0.0340,0.0246</t>
+  </si>
+  <si>
+    <t>0.0294,0.1398,0.9234,0.0227</t>
+  </si>
+  <si>
+    <t>0.0064,0.8141,0.7939,0.0095</t>
+  </si>
+  <si>
+    <t>0.0356,0.7114,0.6601,0.0203</t>
+  </si>
+  <si>
+    <t>0.0090,0.9047,0.2882,0.0372</t>
+  </si>
+  <si>
+    <t>0.0179,0.8710,0.3433,0.0301</t>
+  </si>
+  <si>
+    <t>0.0118,0.0273,0.0048,0.9903</t>
+  </si>
+  <si>
+    <t>0.0046,0.0195,0.0016,0.9961</t>
+  </si>
+  <si>
+    <t>0.0029,0.0320,0.0020,0.9964</t>
+  </si>
+  <si>
+    <t>0.0306,0.0624,0.0055,0.9792</t>
+  </si>
+  <si>
+    <t>0.0049,0.0083,0.0095,0.9929</t>
+  </si>
+  <si>
+    <t>0.0061,0.0295,0.0022,0.9946</t>
+  </si>
+  <si>
+    <t>0.0269,0.8616,0.3152,0.0326</t>
+  </si>
+  <si>
+    <t>0.0083,0.8844,0.5762,0.0150</t>
+  </si>
+  <si>
+    <t>0.0221,0.5912,0.8230,0.0124</t>
+  </si>
+  <si>
+    <t>0.0153,0.2297,0.9198,0.0179</t>
+  </si>
+  <si>
+    <t>0.0125,0.7248,0.7965,0.0048</t>
+  </si>
+  <si>
+    <t>0.0129,0.8098,0.7171,0.0089</t>
+  </si>
+  <si>
+    <t>0.9429,0.0684,0.0094,0.0044</t>
+  </si>
+  <si>
+    <t>0.9616,0.0307,0.0055,0.0073</t>
+  </si>
+  <si>
+    <t>0.9404,0.0755,0.0065,0.0048</t>
+  </si>
+  <si>
+    <t>0.9627,0.0387,0.0047,0.0043</t>
+  </si>
+  <si>
+    <t>0.9750,0.0178,0.0049,0.0041</t>
+  </si>
+  <si>
+    <t>0.9655,0.0318,0.0046,0.0051</t>
+  </si>
+  <si>
+    <t>0.9644,0.0347,0.0051,0.0041</t>
+  </si>
+  <si>
+    <t>0.9644,0.0313,0.0045,0.0046</t>
+  </si>
+  <si>
+    <t>0.9778,0.0130,0.0033,0.0056</t>
+  </si>
+  <si>
+    <t>0.9787,0.0137,0.0034,0.0048</t>
+  </si>
+  <si>
+    <t>0.9832,0.0081,0.0018,0.0052</t>
+  </si>
+  <si>
+    <t>0.9806,0.0105,0.0030,0.0058</t>
+  </si>
+  <si>
+    <t>0.9765,0.0178,0.0040,0.0038</t>
+  </si>
+  <si>
+    <t>0.9717,0.0202,0.0040,0.0064</t>
+  </si>
+  <si>
+    <t>0.9809,0.0101,0.0028,0.0060</t>
+  </si>
+  <si>
+    <t>0.9639,0.0262,0.0052,0.0084</t>
+  </si>
+  <si>
+    <t>0.0006,0.0052,0.9879,0.0355</t>
+  </si>
+  <si>
+    <t>0.1081,0.1088,0.8223,0.0591</t>
+  </si>
+  <si>
+    <t>0.3226,0.1905,0.4489,0.1723</t>
+  </si>
+  <si>
+    <t>0.1098,0.0594,0.8497,0.0470</t>
+  </si>
+  <si>
+    <t>0.0248,0.9615,0.0180,0.0025</t>
+  </si>
+  <si>
+    <t>0.0750,0.9170,0.0153,0.0052</t>
+  </si>
+  <si>
+    <t>0.1328,0.8648,0.0201,0.0058</t>
+  </si>
+  <si>
+    <t>0.1693,0.8486,0.0182,0.0052</t>
+  </si>
+  <si>
+    <t>0.0354,0.9483,0.0131,0.0056</t>
+  </si>
+  <si>
+    <t>0.0228,0.9649,0.0062,0.0033</t>
+  </si>
+  <si>
+    <t>0.1415,0.8692,0.0125,0.0056</t>
+  </si>
+  <si>
+    <t>0.6457,0.2280,0.1358,0.0753</t>
+  </si>
+  <si>
+    <t>0.1532,0.0395,0.8015,0.0800</t>
+  </si>
+  <si>
+    <t>0.1631,0.6786,0.0893,0.2181</t>
+  </si>
+  <si>
+    <t>0.2657,0.1762,0.6187,0.0572</t>
+  </si>
+  <si>
+    <t>0.1602,0.1690,0.0236,0.8493</t>
+  </si>
+  <si>
+    <t>0.0084,0.9767,0.0152,0.0050</t>
+  </si>
+  <si>
+    <t>0.0053,0.9826,0.0072,0.0076</t>
+  </si>
+  <si>
+    <t>0.0559,0.8917,0.0287,0.0314</t>
+  </si>
+  <si>
+    <t>0.0027,0.9825,0.0288,0.0080</t>
+  </si>
+  <si>
+    <t>0.1269,0.8573,0.0498,0.0053</t>
+  </si>
+  <si>
+    <t>0.5462,0.5361,0.0306,0.0101</t>
+  </si>
+  <si>
+    <t>0.4312,0.6476,0.0210,0.0078</t>
+  </si>
+  <si>
+    <t>0.8665,0.1447,0.0340,0.0121</t>
+  </si>
+  <si>
+    <t>0.8092,0.2311,0.0160,0.0145</t>
+  </si>
+  <si>
+    <t>0.9639,0.0163,0.0043,0.0157</t>
+  </si>
+  <si>
+    <t>0.9064,0.0856,0.0162,0.0147</t>
+  </si>
+  <si>
+    <t>0.9540,0.0370,0.0056,0.0089</t>
+  </si>
+  <si>
+    <t>0.6126,0.0690,0.3785,0.0226</t>
+  </si>
+  <si>
+    <t>0.9719,0.0165,0.0042,0.0088</t>
+  </si>
+  <si>
+    <t>0.9670,0.0225,0.0036,0.0084</t>
+  </si>
+  <si>
+    <t>0.0348,0.6835,0.6582,0.0300</t>
+  </si>
+  <si>
+    <t>0.0227,0.5669,0.8357,0.0103</t>
+  </si>
+  <si>
+    <t>0.0641,0.4064,0.7776,0.0318</t>
+  </si>
+  <si>
+    <t>0.0992,0.4150,0.6689,0.0338</t>
+  </si>
+  <si>
+    <t>0.4268,0.1191,0.3468,0.2428</t>
+  </si>
+  <si>
+    <t>0.3709,0.4739,0.1549,0.1066</t>
+  </si>
+  <si>
+    <t>0.3067,0.0549,0.7083,0.0351</t>
+  </si>
+  <si>
+    <t>0.1837,0.1181,0.1122,0.7957</t>
+  </si>
+  <si>
+    <t>0.1026,0.0400,0.0100,0.9426</t>
+  </si>
+  <si>
+    <t>0.0003,0.0043,0.0010,0.9994</t>
+  </si>
+  <si>
+    <t>0.0043,0.0194,0.0027,0.9956</t>
+  </si>
+  <si>
+    <t>0.0181,0.0119,0.0082,0.9854</t>
+  </si>
+  <si>
+    <t>0.0135,0.8847,0.3543,0.0419</t>
+  </si>
+  <si>
+    <t>0.9037,0.1069,0.0160,0.0107</t>
+  </si>
+  <si>
+    <t>0.2247,0.7922,0.0215,0.0095</t>
+  </si>
+  <si>
+    <t>0.8702,0.1420,0.0151,0.0128</t>
+  </si>
+  <si>
+    <t>0.7566,0.3061,0.0136,0.0113</t>
+  </si>
+  <si>
+    <t>0.8504,0.0924,0.0497,0.0602</t>
+  </si>
+  <si>
+    <t>0.3601,0.0480,0.0785,0.6105</t>
+  </si>
+  <si>
+    <t>0.9394,0.0477,0.0120,0.0132</t>
+  </si>
+  <si>
+    <t>0.0038,0.0621,0.3675,0.7788</t>
+  </si>
+  <si>
+    <t>0.7125,0.0269,0.0574,0.2193</t>
+  </si>
+  <si>
+    <t>0.8619,0.0576,0.0326,0.0506</t>
+  </si>
+  <si>
+    <t>0.3220,0.6947,0.0329,0.0198</t>
+  </si>
+  <si>
+    <t>0.7078,0.1968,0.1202,0.0408</t>
+  </si>
+  <si>
+    <t>0.3633,0.6150,0.0674,0.0236</t>
+  </si>
+  <si>
+    <t>0.0535,0.8929,0.0192,0.0442</t>
+  </si>
+  <si>
+    <t>0.4747,0.5273,0.0583,0.0246</t>
+  </si>
+  <si>
+    <t>0.5130,0.4758,0.0713,0.0310</t>
+  </si>
+  <si>
+    <t>0.9679,0.0228,0.0047,0.0075</t>
+  </si>
+  <si>
+    <t>0.9521,0.0507,0.0071,0.0064</t>
+  </si>
+  <si>
+    <t>0.9772,0.0141,0.0027,0.0063</t>
+  </si>
+  <si>
+    <t>0.9779,0.0114,0.0029,0.0071</t>
+  </si>
+  <si>
+    <t>0.9232,0.0675,0.0135,0.0108</t>
+  </si>
+  <si>
+    <t>0.9412,0.0502,0.0046,0.0140</t>
+  </si>
+  <si>
+    <t>0.9739,0.0149,0.0025,0.0086</t>
+  </si>
+  <si>
+    <t>0.9716,0.0158,0.0044,0.0087</t>
+  </si>
+  <si>
+    <t>0.1702,0.8290,0.0391,0.0087</t>
+  </si>
+  <si>
+    <t>0.2925,0.7602,0.0202,0.0079</t>
+  </si>
+  <si>
+    <t>0.2306,0.8064,0.0200,0.0079</t>
+  </si>
+  <si>
+    <t>0.5856,0.4732,0.0369,0.0096</t>
+  </si>
+  <si>
+    <t>0.7889,0.2583,0.0267,0.0092</t>
+  </si>
+  <si>
+    <t>0.7231,0.2611,0.0767,0.0143</t>
+  </si>
+  <si>
+    <t>0.8755,0.1608,0.0143,0.0068</t>
+  </si>
+  <si>
+    <t>0.5862,0.4636,0.0152,0.0204</t>
+  </si>
+  <si>
+    <t>0.0279,0.0966,0.9433,0.0155</t>
+  </si>
+  <si>
+    <t>0.6855,0.3956,0.0202,0.0057</t>
+  </si>
+  <si>
+    <t>0.0199,0.0754,0.9451,0.0221</t>
+  </si>
+  <si>
+    <t>0.0175,0.1366,0.9324,0.0195</t>
+  </si>
+  <si>
+    <t>0.1240,0.0517,0.8817,0.0141</t>
+  </si>
+  <si>
+    <t>0.0143,0.4757,0.8426,0.0213</t>
+  </si>
+  <si>
+    <t>0.0352,0.0364,0.9519,0.0129</t>
+  </si>
+  <si>
+    <t>0.0502,0.0476,0.9311,0.0151</t>
+  </si>
+  <si>
+    <t>0.0457,0.0445,0.9378,0.0141</t>
+  </si>
+  <si>
+    <t>0.2971,0.1220,0.6392,0.0220</t>
+  </si>
+  <si>
+    <t>0.4898,0.2535,0.1810,0.1974</t>
+  </si>
+  <si>
+    <t>0.3999,0.4462,0.1395,0.1088</t>
+  </si>
+  <si>
+    <t>0.0959,0.6153,0.4308,0.0126</t>
+  </si>
+  <si>
+    <t>0.2320,0.5682,0.2225,0.0389</t>
+  </si>
+  <si>
+    <t>0.3834,0.2679,0.3536,0.0532</t>
+  </si>
+  <si>
+    <t>0.4042,0.0759,0.5841,0.0505</t>
+  </si>
+  <si>
+    <t>0.4558,0.2074,0.3729,0.0265</t>
+  </si>
+  <si>
+    <t>0.1432,0.8729,0.0126,0.0046</t>
+  </si>
+  <si>
+    <t>0.4281,0.6632,0.0145,0.0046</t>
+  </si>
+  <si>
+    <t>0.2903,0.7532,0.0198,0.0093</t>
+  </si>
+  <si>
+    <t>0.9084,0.1104,0.0120,0.0079</t>
+  </si>
+  <si>
+    <t>0.7155,0.3640,0.0149,0.0075</t>
+  </si>
+  <si>
+    <t>0.4347,0.2173,0.3609,0.0785</t>
+  </si>
+  <si>
+    <t>0.5692,0.0871,0.3497,0.0563</t>
+  </si>
+  <si>
+    <t>0.4760,0.0719,0.2842,0.2362</t>
+  </si>
+  <si>
+    <t>0.3286,0.0435,0.4912,0.1779</t>
+  </si>
+  <si>
+    <t>0.3620,0.0920,0.4234,0.2442</t>
+  </si>
+  <si>
+    <t>0.0439,0.0833,0.8631,0.1001</t>
+  </si>
+  <si>
+    <t>0.0963,0.2025,0.3605,0.4959</t>
+  </si>
+  <si>
+    <t>0.0397,0.4879,0.6920,0.0684</t>
+  </si>
+  <si>
+    <t>0.0521,0.1292,0.8224,0.1159</t>
+  </si>
+  <si>
+    <t>0.0408,0.4099,0.5544,0.2087</t>
+  </si>
+  <si>
+    <t>0.9685,0.0207,0.0038,0.0086</t>
+  </si>
+  <si>
+    <t>0.9130,0.1020,0.0153,0.0070</t>
+  </si>
+  <si>
+    <t>0.9712,0.0245,0.0038,0.0043</t>
+  </si>
+  <si>
+    <t>0.9667,0.0299,0.0046,0.0047</t>
+  </si>
+  <si>
+    <t>0.9672,0.0222,0.0043,0.0080</t>
+  </si>
+  <si>
+    <t>0.9569,0.0344,0.0046,0.0084</t>
+  </si>
+  <si>
+    <t>0.9806,0.0112,0.0022,0.0060</t>
+  </si>
+  <si>
+    <t>0.9771,0.0136,0.0030,0.0066</t>
+  </si>
+  <si>
+    <t>0.1752,0.0551,0.8496,0.0144</t>
+  </si>
+  <si>
+    <t>0.5998,0.3232,0.1526,0.0226</t>
+  </si>
+  <si>
+    <t>0.5899,0.3124,0.1568,0.0961</t>
+  </si>
+  <si>
+    <t>0.0375,0.0963,0.9150,0.0243</t>
+  </si>
+  <si>
+    <t>0.0093,0.3353,0.8842,0.0304</t>
+  </si>
+  <si>
+    <t>0.1230,0.5024,0.5448,0.0467</t>
+  </si>
+  <si>
+    <t>0.0057,0.0318,0.9798,0.0098</t>
+  </si>
+  <si>
+    <t>0.2622,0.1958,0.6029,0.0346</t>
+  </si>
+  <si>
+    <t>0.0034,0.1453,0.9704,0.0092</t>
+  </si>
+  <si>
+    <t>0.0219,0.1642,0.8740,0.0632</t>
+  </si>
+  <si>
+    <t>0.2169,0.5276,0.2242,0.1750</t>
+  </si>
+  <si>
+    <t>0.2849,0.0632,0.6920,0.0512</t>
+  </si>
+  <si>
+    <t>0.5509,0.1696,0.2356,0.1446</t>
+  </si>
+  <si>
+    <t>0.6183,0.1036,0.2316,0.1271</t>
+  </si>
+  <si>
+    <t>0.9793,0.0174,0.0023,0.0034</t>
+  </si>
+  <si>
+    <t>0.9755,0.0218,0.0029,0.0034</t>
+  </si>
+  <si>
+    <t>0.9797,0.0152,0.0026,0.0041</t>
+  </si>
+  <si>
+    <t>0.8841,0.1432,0.0142,0.0080</t>
+  </si>
+  <si>
+    <t>0.9563,0.0328,0.0079,0.0081</t>
+  </si>
+  <si>
+    <t>0.9310,0.0734,0.0103,0.0073</t>
+  </si>
+  <si>
+    <t>0.9706,0.0224,0.0057,0.0049</t>
+  </si>
+  <si>
+    <t>0.9639,0.0354,0.0050,0.0049</t>
+  </si>
+  <si>
+    <t>0.0695,0.1171,0.8240,0.0858</t>
+  </si>
+  <si>
+    <t>0.0276,0.1667,0.8612,0.0692</t>
+  </si>
+  <si>
+    <t>0.0156,0.1432,0.9382,0.0159</t>
+  </si>
+  <si>
+    <t>0.1164,0.1678,0.8003,0.0298</t>
+  </si>
+  <si>
+    <t>0.0088,0.0208,0.9528,0.0599</t>
+  </si>
+  <si>
+    <t>0.1565,0.0474,0.6937,0.2025</t>
+  </si>
+  <si>
+    <t>0.2376,0.2606,0.5273,0.1934</t>
+  </si>
+  <si>
+    <t>0.0209,0.2886,0.4524,0.4161</t>
+  </si>
+  <si>
+    <t>0.7855,0.0184,0.0330,0.1585</t>
+  </si>
+  <si>
+    <t>0.0071,0.3189,0.0036,0.9731</t>
+  </si>
+  <si>
+    <t>0.0294,0.0386,0.0033,0.9820</t>
+  </si>
+  <si>
+    <t>0.0048,0.0126,0.0021,0.9960</t>
+  </si>
+  <si>
+    <t>0.0039,0.0072,0.0021,0.9966</t>
+  </si>
+  <si>
+    <t>0.0849,0.0894,0.0261,0.9297</t>
   </si>
 </sst>
 </file>
@@ -1956,10 +1959,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1987,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2127,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,10 +2183,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2267,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,10 +2309,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2368,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2382,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2435,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2449,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2480,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,10 +2533,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2816,7 @@
         <v>262</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,10 +2855,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2914,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2928,7 @@
         <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,10 +2939,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +2998,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3096,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3124,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3135,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,10 +3149,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3163,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3429,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3558,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3586,7 @@
         <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3597,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3614,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3670,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3695,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3709,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3838,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3852,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3863,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,10 +3891,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3905,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4003,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4034,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4059,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4090,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4118,7 @@
         <v>260</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4160,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4188,7 @@
         <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4202,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,10 +4213,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,10 +4227,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4356,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4367,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4384,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4398,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,10 +4451,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,10 +4605,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4622,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4633,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4650,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4661,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4706,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4720,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4734,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4759,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4773,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4801,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4829,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,10 +4857,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4902,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5042,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,10 +5095,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,10 +5165,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5179,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5193,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,10 +5333,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5403,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,10 +5431,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5518,7 @@
         <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
